--- a/Packages/cn.etetet.excel/Luban/Config/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.excel/Luban/Config/Base/__tables__.xlsx
@@ -119,7 +119,7 @@
     <t>Text</t>
   </si>
   <si>
-    <t>../../../../cn.etetet.quest/Luban/Config/Datas/Text.xlsx,../../../../cn.etetet.wow/Luban/Config/Datas/Text.xlsx,../../../../cn.etetet.spell/Luban/Config/Datas/Text.xlsx</t>
+    <t>../../../../cn.etetet.quest/Luban/Config/Datas/Text.xlsx,../../../../cn.etetet.statesync/Luban/Config/Datas/Text.xlsx,../../../../cn.etetet.spell/Luban/Config/Datas/Text.xlsx</t>
   </si>
 </sst>
 </file>
